--- a/NY_State_Reports_2026-10-23/Fanatics_Weekly_Report.xlsx
+++ b/NY_State_Reports_2026-10-23/Fanatics_Weekly_Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\MOBILE SPORTS WAGERING\11_Weekly Web Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B23711AD-3E04-4D66-BF33-69D7BEF19A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD935C4A-D0CB-4123-B2F9-61B6C7F94AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EDA5EF8F-B63B-4D9E-966F-AB4A019BBE74}"/>
   </bookViews>
@@ -2975,7 +2975,12 @@
         <v>46313</v>
       </c>
       <c r="B42" s="20"/>
-      <c r="F42" s="33"/>
+      <c r="C42" s="21">
+        <v>68446034.360000014</v>
+      </c>
+      <c r="F42" s="33">
+        <v>5844851.1700000009</v>
+      </c>
       <c r="G42"/>
       <c r="H42"/>
       <c r="I42"/>
@@ -3495,11 +3500,11 @@
       </c>
       <c r="C67" s="23">
         <f>SUM(C13:C66)</f>
-        <v>1675849923.7600005</v>
+        <v>1744295958.1200004</v>
       </c>
       <c r="F67" s="23">
         <f>SUM(F13:F66)</f>
-        <v>118965815.02</v>
+        <v>124810666.19</v>
       </c>
       <c r="G67"/>
       <c r="H67"/>
